--- a/src_files/data_files/emissiondata_maf2020.xlsx
+++ b/src_files/data_files/emissiondata_maf2020.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\backbone\north_european_model (2IMatch)\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925790C0-EADE-48EE-8182-E38B41CD96D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4BF835-BDBB-464C-ABA4-0AAEAF7A0307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="17520" xr2:uid="{3E3DEAD5-6055-4DB8-B424-EEC0B5E366CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3E3DEAD5-6055-4DB8-B424-EEC0B5E366CE}"/>
   </bookViews>
   <sheets>
     <sheet name="emissiondata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>CO2</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>group</t>
-  </si>
-  <si>
-    <t>H2 balanced</t>
   </si>
   <si>
     <t>ETS-CO2</t>
@@ -503,7 +500,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>105</v>
@@ -520,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>140</v>
@@ -537,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>120</v>
@@ -554,28 +551,14 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>2035</v>
-      </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>105</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
